--- a/downloads/[取得或處分私募有價證券公告]_整合總表.xlsx
+++ b/downloads/[取得或處分私募有價證券公告]_整合總表.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,37 +471,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>代子公司JOYSTAR INTERNATIONAL CO.,LTd公告取得私募有價證券VTeam Siegfried Supply Chain Finance Fund</t>
+          <t>公告本公司取得私募有價證券Siegfried Supply Chain Finance Fund</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>VTeam Siegfried Supply Chain Finance Fund私募有價證券</t>
+          <t>VTeam Siegfried Supply Chain Finance Fund S.C.A. SICAV-SIF - Series 1 Class A 股份； 性質為私募有價證券</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>民國115年02月23日</t>
+          <t>民國115年03月02日</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>(A)交易數量：不適用 (B)每單位價格：不適用 (C)交易總金額：US$5,000,000</t>
+          <t>(A)交易數量：不適用 (B)每單位價格：不適用 (C)交易總金額：US$2,000,000元</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JOYSTAR INTERNATIONAL CO.,LTd持有本交易證券情形： (A)數量：不適用 (B)累積持有總金額：US$22,614,240 (C)持股比例：不適用 (D)權利受限情形：無</t>
+          <t>(A)數量：不適用 (B)累積持有總金額：US$2,000,000 (C)持股比例：不適用 (D)權利受限情形：無</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>該子公司私募有價證券投資： (A)占母公司最近期個體財務報表總資產比例：4.94% (B)占最近期合併財務報表歸屬於母公司業主之權益比例：8.90% (C)母公司最近期個體財務報表中營運資金：新台幣 -979,473仟元</t>
+          <t>(A)占母公司最近期個體財務報表總資產比例：11.13% (B)占最近期合併財務報表歸屬於母公司業主之權益比例：11.60% (C)母公司最近期個體財務報表中營運資金：NT$410,483仟元</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -516,579 +516,163 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>該子公司無資金不足，仍取得有價證券之情形。</t>
+          <t>無</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>4749</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>代子公司JOYSTAR INTERNATIONAL CO.,LTd公告取得私募有價證券VTeam Siegfried Supply Chain Finance Fund</t>
+          <t>公告本公司決議取得私募有價證券(更正誤用第二十款)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VTeam Siegfried Supply Chain Finance Fund私募有價證券</t>
+          <t>富宸材料國際股份有限公司國內第一次無擔保可轉換公司債</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>民國115年04月24日</t>
+          <t>民國115年05月08日</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(A)交易數量：不適用 (B)每單位價格：不適用 (C)交易總金額：US$4,400,000</t>
+          <t>交易單位數量：3,060張 每單位價格：新臺幣100,000元整 交易總金額：新臺幣306,000,000元整</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>JOYSTAR INTERNATIONAL CO.,LTd持有本交易證券情形： (A)數量：不適用 (B)累積持有總金額：US$27,014,240 (C)持股比例：不適用 (D)權利受限情形：無</t>
+          <t>累積持有數量: 3,060張 累積持有金額：新台幣306,000,000元 持股比例：不適用 權利受限情形：無</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>該子公司私募有價證券投資： (A)占母公司最近期個體財務報表總資產比例：4.39% (B)占最近期合併財務報表歸屬於母公司業主之權益比例：7.55% (C)母公司最近期個體財務報表中營運資金：新台幣-581,744仟元</t>
+          <t>占總資產比例：2.81% 占業主權益比例：3.42% 營運資金數額：新台幣 3,890,444 仟元</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>無</t>
+          <t>不適用</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>投資理財</t>
+          <t>經營策略規劃</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>該子公司無資金不足，仍取得有價證券之情形。</t>
+          <t>更正115/5/8公告款式及內容</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>代元大韓國公告取得Korea Real Estate Investment &amp; Trust Co., Ltd發行之第49次私募可交換公司債</t>
+          <t>公告本公司處分第一金全球優先擔保債券私募基金</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Korea Real Estate Investment &amp; Trust Co., Ltd第49次私募可交換公司債 (Exchangeable Bond)</t>
+          <t>名稱：第一金全球優先擔保債券私募基金 性質：私募基金</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>民國115年01月15日</t>
+          <t>民國115年04月15日</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>交易單位數量：200,000單位 每單位價格：韓圜10,000元 交易總金額：韓圜20億元</t>
+          <t>(1)交易單位數量：150,000單位 (2)每單位價格：美金12.5654元 (3)交易總金額：美金1,884,810元，新台幣約59,584,499元</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>累積數量：200,000單位 累積金額：韓圜20億元 持股比例：10.0% 權利受限情形：無</t>
+          <t>累積持有本交易證券（含本次交易）之數量：150,000單位 金額：美金1,500,000元 持股比例及權利受限情形：無</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>總資產比率：2.21% 股東權益比率：2.57% 營運資金：不適用</t>
+          <t>(1)占公司最近期財務報表中總資產：0.074% (2)歸屬於母公司業主之權益之比例：0.16% (3)最近期財務報表中營運資金數額：1,172,556仟元</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>支付予證券經紀商本案交易總金額之1.0%(韓圜20,000,000元)，作為經紀費用。</t>
+          <t>信託管理費0.2%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>業務需要</t>
+          <t>投資理財</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>本公告匯率換算以韓圜兌新臺幣1:0.02145為準。</t>
+          <t>每單位價格及交易總金額，依據基金公司目前提供之淨值計算， 實際交易淨值確認後將進行補充公告。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>元大金控代子公司元大儲蓄銀行(韓國)公告取得Daishin Asset Trust Co., Ltd.發行之私募公司債</t>
+          <t>公告本公司處分第一金全球優先擔保債券私募基金(補充公告)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Daishin Asset Trust Co., Ltd.發行之私募公司債</t>
+          <t>名稱：第一金全球優先擔保債券私募基金 性質：私募基金</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>民國115年01月23日</t>
+          <t>民國115年04月15日</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>交易單位：300,000單位 發行票面價：韓圜 10,000元 預計交易總金額：韓圜 3,000,000,000元</t>
+          <t>(1)交易單位數量：150,000單位 (2)每單位價格：美金12.5993元 (3)交易總金額：美金1,889,895元，新台幣約59,626,187元</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>累積數量：300,000單位 累積總金額：韓圜 3,000,000,000元 持股比例：4.29% 權利受限情形：無</t>
+          <t>累積持有本交易證券（含本次交易）之數量：150,000單位 金額：美金1,500,000元 持股比例及權利受限情形：無</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>總資產比率：0.15% 股東權益比率：0.18% 營運資金：不適用</t>
+          <t>(1)占公司最近期財務報表中總資產：0.074% (2)歸屬於母公司業主之權益之比例：0.16% (3)最近期財務報表中營運資金數額：1,172,556仟元</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>無</t>
+          <t>信託管理費0.2%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>業務需求</t>
+          <t>投資理財</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>本公告匯率換算以韓圜兌新台幣為0.021474為準</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>元大金控代子公司元大儲蓄銀行(韓國)公告取得Korea Rental Co., Ltd.發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Korea Rental Co., Ltd.發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>民國115年02月23日</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>交易單位：1單位 發行票面價： 韓圜 3,000,000,000元 預計交易總金額：韓圜 3,000,000,000元</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>累積數量：1單位 累積總金額：韓圜 3,000,000,000元 持股比例：30% 權利受限情形：無</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>總資產比率：0.17% 股東權益比率：0.20% 營運資金：不適用</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>業務需求</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>本公告匯率換算以韓圜兌新台幣為0.021601為準</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>元大金控代元大證券(韓國)公告取得KOLON CORPORATIOIN發行之第256次私募可交換公司債</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>KOLON CORPORATION第256次私募可交換公司債 (Exchangeable Bond)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>民國115年03月06日</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>交易單位數量：300,000單位 每單位價格：韓圜10,000元 交易總金額：韓圜30億元</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>累積數量：300,000單位 累積金額：韓圜30億元 持股比例：5.0% 權利受限情形：無</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>總資產比率：2.28% 股東權益比率：2.65% 營運資金：不適用</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>支付予證券經紀商本案交易總金額之2.0%(韓圜60,000,000元)，作為經紀費用。</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>業務需要</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>本公告匯率換算以韓圜兌新臺幣1:0.021618為準。</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>元大金控代子公司元大儲蓄銀行(韓國)公告取得Ssangyong C&amp;E Co., Ltd.發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ssangyong C&amp;E Co., Ltd.發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>民國115年03月20日</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>交易單位：1單位 發行票面價： 韓圜 4,000,000,000元 預計交易總金額：韓圜 4,000,000,000元</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>累積數量：1單位 累積總金額：韓圜 4,000,000,000元 持股比例：8.00% 權利受限情形：無</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>總資產比率：0.19% 股東權益比率：0.22% 營運資金：不適用</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>業務需求</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>本公告匯率換算以韓圜兌新台幣為0.021618為準</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>元大金控代子公司元大儲蓄銀行(韓國)公告取得IGIS Asset Management Co., Ltd.發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>IGIS Asset Management Co., Ltd.發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>民國115年04月24日</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>交易單位：1單位 發行票面價：韓圜 4,000,000,000元 預計交易總金額：韓圜 4,000,000,000元</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>累積數量：1單位 累積總金額：韓圜 4,000,000,000元 持股比例：100.00% 權利受限情形：無</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>總資產比率：0.21% 股東權益比率：0.24% 營運資金：不適用</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>業務需求</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>本公告匯率換算以韓圜兌新台幣為0.02144為準</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2885</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>元大金控代子公司元大儲蓄銀行(韓國)公告取得Huvis Corporation發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Huvis Corporation發行之私募公司債</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>民國115年05月08日</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>交易單位：1單位 發行票面價：韓圜 2,000,000,000元 預計交易總金額：韓圜 2,000,000,000元</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>累積數量：1單位 累積總金額：韓圜 2,000,000,000元 持股比例：25.00% 權利受限情形：無</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>總資產比率：0.22% 股東權益比率：0.25% 營運資金：不適用</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>業務需求</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>本公告匯率換算以韓圜兌新台幣為0.021409為準</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>代子公司Wisdom Bright Inc.公告取得私募有價證券VTeam Siegfried Supply Chain Finance Fund</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>VTeam Siegfried Supply Chain Finance Fund私募有價證券</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>民國115年01月26日</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>(A)交易數量：不適用 (B)每單位價格：不適用 (C)交易總金額：USD$5,000,000</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Wisdom Bright Inc.持有本交易證券情形： (A)數量：不適用 (B)累積持有總金額：USD$11,000,000 (C)持股比例：不適用 (D)權利受限情形：無</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>該子公司私募有價證券投資： (A)占母公司最近期個體財務報表總資產比例：36.07% (B)占最近期合併財務報表歸屬於母公司業主之權益比例：49.01% (C)母公司最近期個體財務報表中營運資金：761,620仟元</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>投資理財</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>3257</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>代子公司Wisdom Bright Inc.公告取得私募有價證券VTeam Siegfried Supply Chain Finance Fund</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>VTeam Siegfried Supply Chain Finance Fund私募有價證券</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>民國115年04月15日</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>(A)交易數量：不適用 (B)每單位價格：不適用 (C)交易總金額：US$2,900,000元</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Wisdom Bright Inc.持有本交易證券情形： (A)數量：不適用 (B)累積持有總金額：US$13,900,000元 (C)持股比例：不適用 (D)權利受限情形：無</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>該子公司私募有價證券投資： (A)占母公司最近期個體財務報表總資產比例：38.07% (B)占最近期合併財務報表歸屬於母公司業主之權益比例：52.44% (C)母公司最近期個體財務報表中營運資金：NT$ 906,744仟元</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>投資理財</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>無</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>4961</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>代重要子公司深圳天德鈺科技股份有限公司公告取得私募有價證券</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>華西證券華彩專享添盈1號單-資產管理計畫</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>民國115年05月22日</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>本次交易單位數量:不適用 每單位價格:不適用 交易總金額:人民幣2億元</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>累積持有本交易證券（含本次交易）之數量:不適用 金額:人民幣2億元 持股比例:不適用 權利受限情形:無</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>佔總資產比例: 4.73% 佔歸屬於母公司業主權益比例: 5.25% 營運資金數額:新台幣6,939,124仟元</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>依合約規定</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>提高資金使用效率</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>無</t>
+          <t>依基金成交淨值補充公告</t>
         </is>
       </c>
     </row>
